--- a/data/2025/30-olt/125347-slatina/budget_file.xlsx
+++ b/data/2025/30-olt/125347-slatina/budget_file.xlsx
@@ -49557,35 +49557,35 @@
       </c>
     </row>
     <row r="2331">
-      <c r="A2331" t="inlineStr">
+      <c r="A2331" s="2" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="C2331" s="6" t="inlineStr">
+      <c r="B2331" s="2" t="n"/>
+      <c r="C2331" s="3" t="inlineStr">
         <is>
           <t>ACHIZITIONARE IMOBIL MAGAZINUL OLTUL</t>
         </is>
       </c>
-      <c r="E2331" t="n">
+      <c r="D2331" s="2" t="n"/>
+      <c r="E2331" s="2" t="n">
         <v>147</v>
       </c>
-      <c r="F2331" t="inlineStr"/>
-      <c r="G2331" s="5" t="n">
+      <c r="F2331" s="2" t="inlineStr"/>
+      <c r="G2331" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H2331" s="5" t="n"/>
-      <c r="I2331" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J2331" t="inlineStr">
-        <is>
-          <t>llm:gemini-3.6-flash</t>
-        </is>
-      </c>
-      <c r="K2331" t="inlineStr">
-        <is>
-          <t>cell re-read from image (unverified transcription)</t>
+      <c r="H2331" s="4" t="n"/>
+      <c r="I2331" s="4" t="n"/>
+      <c r="J2331" s="2" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="K2331" s="2" t="inlineStr">
+        <is>
+          <t>unparseable cell 'I' in column valoare_an_curent</t>
         </is>
       </c>
     </row>
@@ -54216,7 +54216,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -54262,40 +54262,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>total_2026</t>
+        </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>unparseable-cell pass p4: 0 cells recovered</t>
+          <t>unparseable cell 'TOTALVENITURI 00.01' in column total_2026</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>147</v>
+        <v>3</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>total_2026</t>
+        </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>unparseable-cell pass p147: 1 cells recovered</t>
+          <t>unparseable cell 'TOTAL CHELTUIELI' in column total_2026</t>
         </is>
       </c>
     </row>
@@ -54320,7 +54330,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>unparseable cell 'TOTALVENITURI 00.01' in column total_2026</t>
+          <t>unparseable cell 'DEFICIT 63551' in column total_2026</t>
         </is>
       </c>
     </row>
@@ -54345,7 +54355,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>unparseable cell 'TOTAL CHELTUIELI' in column total_2026</t>
+          <t>unparseable cell 'Buget 2025' in column total_2026</t>
         </is>
       </c>
     </row>
@@ -54370,7 +54380,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>unparseable cell 'DEFICIT 63551' in column total_2026</t>
+          <t>unparseable cell 'TOTALVENITURI SE' in column total_2026</t>
         </is>
       </c>
     </row>
@@ -54386,7 +54396,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -54395,7 +54405,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>unparseable cell 'Buget 2025' in column total_2026</t>
+          <t>unparseable cell 'TOTALCHELTUIELI SE 313.807' in column total_2026</t>
         </is>
       </c>
     </row>
@@ -54411,7 +54421,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -54420,7 +54430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>unparseable cell 'TOTALVENITURI SE' in column total_2026</t>
+          <t>unparseable cell 'TOTALVENITURI SD 00.01 109932' in column total_2026</t>
         </is>
       </c>
     </row>
@@ -54445,7 +54455,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>unparseable cell 'TOTALCHELTUIELI SE 313.807' in column total_2026</t>
+          <t>unparseable cell 'TOTAL CHELTUIELI SD' in column total_2026</t>
         </is>
       </c>
     </row>
@@ -54470,7 +54480,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>unparseable cell 'TOTALVENITURI SD 00.01 109932' in column total_2026</t>
+          <t>unparseable cell '·54.030' in column total_2026</t>
         </is>
       </c>
     </row>
@@ -54486,66 +54496,66 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>147</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>total_2026</t>
+          <t>valoare_an_curent</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>unparseable cell 'TOTAL CHELTUIELI SD' in column total_2026</t>
+          <t>unparseable cell 'mii lei 139' in column valoare_an_curent</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+        <v>147</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>unparseable cell '·54.030' in column total_2026</t>
+          <t>name mismatch vs nomenclator (39%): 'SISTEM INFORMATIC INTEGRAT PENTRU EMITER' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>147</v>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>valoare_an_curent</t>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>11.02</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>unparseable cell 'mii lei 139' in column valoare_an_curent</t>
+          <t>name mismatch vs nomenclator (35%): 'CENTRALA TERMICA GPP ION CREANGA (PLITE)' vs 'Sume defalcate din TVA'</t>
         </is>
       </c>
     </row>
@@ -54565,12 +54575,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12.02</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (39%): 'SISTEM INFORMATIC INTEGRAT PENTRU EMITER' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
+          <t>name mismatch vs nomenclator (40%): 'CENTRALA TERMICA GPP4' vs 'Alte impozite si taxe generale pe bunuri'</t>
         </is>
       </c>
     </row>
@@ -54590,12 +54600,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>15.02</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (35%): 'CENTRALA TERMICA GPP ION CREANGA (PLITE)' vs 'Sume defalcate din TVA'</t>
+          <t>name mismatch vs nomenclator (28%): 'VENTILATOR SI HOTA INDUSTRIALA GRADINITA' vs 'Taxe pe servicii specifice'</t>
         </is>
       </c>
     </row>
@@ -54615,12 +54625,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>12.02</t>
+          <t>16.02</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (40%): 'CENTRALA TERMICA GPP4' vs 'Alte impozite si taxe generale pe bunuri'</t>
+          <t>name mismatch vs nomenclator (39%): 'COS DE FUM PENTRU SCOALA GIMNAZIALA NICO' vs 'Taxe pe utilizarea bunurilor, autorizare'</t>
         </is>
       </c>
     </row>
@@ -54640,12 +54650,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>15.02</t>
+          <t>18.02</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (28%): 'VENTILATOR SI HOTA INDUSTRIALA GRADINITA' vs 'Taxe pe servicii specifice'</t>
+          <t>name mismatch vs nomenclator (34%): 'TREI CENTRALE IN CONDENSARE CU ACCESORII' vs 'Alte impozite si taxe fiscale'</t>
         </is>
       </c>
     </row>
@@ -54665,92 +54675,37 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>16.02</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (39%): 'COS DE FUM PENTRU SCOALA GIMNAZIALA NICO' vs 'Taxe pe utilizarea bunurilor, autorizare'</t>
+          <t>name mismatch vs nomenclator (38%): 'ECHIPAMENTE CANTINA COLEGIUL NATIONAL IO' vs 'TITLUL II  BUNURI SI SERVICII'</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>147</v>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>18.02</t>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>valoare_an_curent</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (34%): 'TREI CENTRALE IN CONDENSARE CU ACCESORII' vs 'Alte impozite si taxe fiscale'</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>147</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (38%): 'ECHIPAMENTE CANTINA COLEGIUL NATIONAL IO' vs 'TITLUL II  BUNURI SI SERVICII'</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>info</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>147</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>valoare_an_curent</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>cell re-read from image (unverified transcription)</t>
+          <t>unparseable cell 'I' in column valoare_an_curent</t>
         </is>
       </c>
     </row>
@@ -54765,7 +54720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -54787,7 +54742,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Documente</t>
+          <t>Schema calitate</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -54797,72 +54752,230 @@
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>Linii de date</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>75</v>
+          <t>Metrica de calitate</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>observed_strict_line_rate</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Linii fara probleme</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>67</v>
+          <t>Recall masurat</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>nu</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>% curat</t>
+          <t>Documente</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>89.3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Erori</t>
+          <t>Linii de date</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Avertismente</t>
+          <t>Linii strict verificate</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Modele LLM folosite</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>gemini-3.6-flash</t>
-        </is>
+          <t>% linii strict verificate</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>89.3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
+          <t>Celule numerice</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Celule numerice strict verificate</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>% celule numerice strict verificate</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>81.3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Pagini asteptate</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Pagini selectate</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Pagini procesate</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>PDF complet</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Linii fara probleme</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>% curat</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>89.3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Erori</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Avertismente</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Informatii</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Schema publicare</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Bundle conversie</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>bdb06712f422faea3a972496</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>SHA-256 PDF sursa</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>fd8ea4e95b61309967ed545fb3ca5d8f0a0e11901c4729d12ed09f6dc41303f7</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
           <t>— Anexa (de la pagina 3)</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>local, pag. 3-163, 2554 linii</t>
         </is>
